--- a/DOSSIES_MULTIFORMATO/IPAAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/IPAAM/dossie.xlsx
@@ -808,7 +808,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021NE0000843</t>
+          <t>2021NE0000842</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19975.87</v>
+        <v>2511.79</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -827,14 +827,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 0253/2021, FACE O ENCERRAMENTO DO EXERCÍCIO DE 2021.</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 0007/2021, FACE O ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021NE0000842</t>
+          <t>2021NE0000843</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2511.79</v>
+        <v>19975.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -853,14 +853,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 0007/2021, FACE O ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 0253/2021, FACE O ENCERRAMENTO DO EXERCÍCIO DE 2021.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2016NE01996</t>
+          <t>2016NE02007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17155.51</v>
+        <v>6540</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2016NE02002</t>
+          <t>2016NE02006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8332.77</v>
+        <v>8953.559999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2016NE02006</t>
+          <t>2016NE02002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8953.559999999999</v>
+        <v>8332.77</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016NE02007</t>
+          <t>2016NE01996</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6540</v>
+        <v>17155.51</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1054,14 +1054,10 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2019NE00814</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2019NE00813</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>28/08/2019</t>
@@ -1077,17 +1073,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso gestor conteúdo Web, objetivando a publicação de notícias, vídeos e imagens via Website.</t>
+          <t>ANULAÇÃO TOTAL PARA ACERTO NA MODALIDADE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2019NE00813</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>2019NE00814</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>28/08/2019</t>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA ACERTO NA MODALIDADE</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso gestor conteúdo Web, objetivando a publicação de notícias, vídeos e imagens via Website.</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024NE0000127</t>
+          <t>2024NE0000131</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18283.02</v>
+        <v>1730.46</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1223,19 +1223,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024NE0000128</t>
+          <t>2024NE0000130</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3530.7</v>
+        <v>31184.56</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024NE0000130</t>
+          <t>2024NE0000128</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31184.56</v>
+        <v>3530.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1313,19 +1313,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024NE0000131</t>
+          <t>2024NE0000127</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1730.46</v>
+        <v>18283.02</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024NE0001696</t>
+          <t>2024NE0001699</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>52990.96</v>
+        <v>3.36</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anulação do saldo da Nota de Empenho n.º 381 do Contrato n.º 007/21, por ocasião do encerramento do Exercício de 2024.</t>
+          <t>Anulação do saldo da Nota de Empenho n.º 10 do Contrato n.º 014/2020 4º Termo Aditivo, por ocasião do encerramento do Exercício de 2024.</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024NE0001699</t>
+          <t>2024NE0001696</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.36</v>
+        <v>52990.96</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1421,17 +1421,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anulação do saldo da Nota de Empenho n.º 10 do Contrato n.º 014/2020 4º Termo Aditivo, por ocasião do encerramento do Exercício de 2024.</t>
+          <t>Anulação do saldo da Nota de Empenho n.º 381 do Contrato n.º 007/21, por ocasião do encerramento do Exercício de 2024.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2017NE00885</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>2017NE00882</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>26/06/2017</t>
@@ -1447,7 +1451,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>Contratação de serviços de tecnologia da informação, incluindo aquisição de softwares, licenças, implantação, manutenção, capacitação e suporte técnico.</t>
         </is>
       </c>
     </row>
@@ -1484,14 +1488,10 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2017NE00882</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2017NE00885</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>26/06/2017</t>
@@ -1507,19 +1507,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da informação, incluindo aquisição de softwares, licenças, implantação, manutenção, capacitação e suporte técnico.</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025NE0000332</t>
+          <t>2025NE0000333</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4220.39</v>
+        <v>12057.66</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1537,19 +1537,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025NE0000333</t>
+          <t>2025NE0000332</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12057.66</v>
+        <v>4220.39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,10 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2017NE00546</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2017NE00545</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>25/04/2017</t>
@@ -1683,17 +1679,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Solicitação de cota para desenvolvimento de sistema de informações geográficas com base em plataforma Esri ArcGIS.</t>
+          <t>ANULAÇÃO TOTAL PARA MUDANÇA NA MODALIDADE.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2017NE00545</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>2017NE00546</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>25/04/2017</t>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA MUDANÇA NA MODALIDADE.</t>
+          <t>Solicitação de cota para desenvolvimento de sistema de informações geográficas com base em plataforma Esri ArcGIS.</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2023NE0001284</t>
+          <t>2023NE0001283</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>865.23</v>
+        <v>14033.05</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1821,19 +1821,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2023NE0001283</t>
+          <t>2023NE0001284</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14033.05</v>
+        <v>865.23</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024NE0000381</t>
+          <t>2024NE0000382</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13102.83</v>
+        <v>22635</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024NE0000382</t>
+          <t>2024NE0000381</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>22635</v>
+        <v>13102.83</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2027,21 +2027,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018NE00376</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00375</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>23/03/2018</t>
@@ -2057,7 +2053,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Solicitação de cota para emissão de empenho com regularização da Natureza da Despesa conforme Orientação Técnica n.º 012/2018 SEFAZ. Termo de Contrato 003/2017 1º Termo Aditivo.</t>
+          <t>ANULAÇÃO PARA ACERTO NA MODALIDADE</t>
         </is>
       </c>
     </row>
@@ -2094,10 +2090,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018NE00375</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>2018NE00376</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>23/03/2018</t>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA ACERTO NA MODALIDADE</t>
+          <t>Solicitação de cota para emissão de empenho com regularização da Natureza da Despesa conforme Orientação Técnica n.º 012/2018 SEFAZ. Termo de Contrato 003/2017 1º Termo Aditivo.</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025NE0001340</t>
+          <t>2025NE0001339</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14/2025</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>65479.2</v>
+        <v>941.6900000000001</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação, compreendendo a hospedagem de sistemas de informação em ambiente de infraestrutura virtualizada, para comport</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025NE0001339</t>
+          <t>2025NE0001340</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>14/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>941.6900000000001</v>
+        <v>65479.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação, compreendendo a hospedagem de sistemas de informação em ambiente de infraestrutura virtualizada, para comport</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024NE0000371</t>
+          <t>2024NE0000368</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1730.46</v>
+        <v>294.23</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2259,19 +2259,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024NE0000370</t>
+          <t>2024NE0000367</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>31184.56</v>
+        <v>5180.29</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024NE0000367</t>
+          <t>2024NE0000370</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5180.29</v>
+        <v>31184.56</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2349,19 +2349,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024NE0000368</t>
+          <t>2024NE0000371</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>294.23</v>
+        <v>1730.46</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2379,19 +2379,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2021NE0000129</t>
+          <t>2021NE0000130</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>78510.72</v>
+        <v>15161.52</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2409,19 +2409,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo WEB, para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2021NE0000130</t>
+          <t>2021NE0000129</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15161.52</v>
+        <v>78510.72</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo WEB, para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2023NE0001112</t>
+          <t>2023NE0001111</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>865.23</v>
+        <v>16112</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2577,14 +2577,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE nº 005 devido a supressão do contrato nº 018/2021, em conformidade com o Decreto Estadual nº 47.925 de 16 de agosto de 2023</t>
+          <t>Anulação parcial da NE nº 001 devido a supressão do contrato 014/2020, em conformidade com o Decreto Estadual nº 47.925 de 16 de agosto de 2023</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2023NE0001111</t>
+          <t>2023NE0001112</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16112</v>
+        <v>865.23</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2603,14 +2603,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE nº 001 devido a supressão do contrato 014/2020, em conformidade com o Decreto Estadual nº 47.925 de 16 de agosto de 2023</t>
+          <t>Anulação parcial da NE nº 005 devido a supressão do contrato nº 018/2021, em conformidade com o Decreto Estadual nº 47.925 de 16 de agosto de 2023</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2018NE01334</t>
+          <t>2018NE01333</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4500.54</v>
+        <v>10000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2018NE01333</t>
+          <t>2018NE01334</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10000</v>
+        <v>4500.54</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2015NE01823</t>
+          <t>2015NE01799</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2015NE01799</t>
+          <t>2015NE01823</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2023NE0000423</t>
+          <t>2023NE00423</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 007/2021 AD: 02.</t>
+          <t>2º TA do Contrato 007/2021 - Serviços de Informática de Forma Eventual.</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2023NE00423</t>
+          <t>2023NE0000423</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2857,19 +2857,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2º TA do Contrato 007/2021 - Serviços de Informática de Forma Eventual.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 007/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2022NE0000351</t>
+          <t>2022NE0000350</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>157480.91</v>
+        <v>85919.97</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2887,19 +2887,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de Serviços de Tecnologia da Informação,compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada para atender as necessidad</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2022NE0000350</t>
+          <t>2022NE0000351</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>85919.97</v>
+        <v>157480.91</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada na prestação de Serviços de Tecnologia da Informação,compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada para atender as necessidad</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2017NE01592</t>
+          <t>2017NE01596</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8.49</v>
+        <v>293640.88</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2973,14 +2973,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2017NE01596</t>
+          <t>2017NE01592</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>293640.88</v>
+        <v>8.49</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
@@ -3058,21 +3058,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2017NE00531</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2017NE00532</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>18/04/2017</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>293640.88</v>
+        <v>15060</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3081,24 +3077,28 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Solicitação de cota para desenvolvimento de sistema de informações geográficas com base em plataforma Esri ArcGIS.</t>
+          <t>ANULAÇÃO TOTAL FACE A RESCISÃO DO CONTRATO 011/2016.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2017NE00532</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>2017NE00531</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>18/04/2017</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>15060</v>
+        <v>293640.88</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3107,14 +3107,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL FACE A RESCISÃO DO CONTRATO 011/2016.</t>
+          <t>Solicitação de cota para desenvolvimento de sistema de informações geográficas com base em plataforma Esri ArcGIS.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2023NE0001087</t>
+          <t>2023NE0001088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2353.8</v>
+        <v>22635</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3133,14 +3133,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE nº 270, devido a supressão do contrato 008/2021, em conformidade com o Decreto Estadual nº 47.925 de 16 de agosto de 2023</t>
+          <t>Anulação parcial da NE nº 479, devido a supressão do contrato 010/2021, em conformidade com o Decreto Estadual 47.925 de 16 de agosto de 2023</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2023NE0001088</t>
+          <t>2023NE0001087</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>22635</v>
+        <v>2353.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE nº 479, devido a supressão do contrato 010/2021, em conformidade com o Decreto Estadual 47.925 de 16 de agosto de 2023</t>
+          <t>Anulação parcial da NE nº 270, devido a supressão do contrato 008/2021, em conformidade com o Decreto Estadual nº 47.925 de 16 de agosto de 2023</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024NE0001123</t>
+          <t>2024NE0001120</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>31184.56</v>
+        <v>18283.02</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3219,19 +3219,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024NE0001122</t>
+          <t>2024NE0001121</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>33952.5</v>
+        <v>3530.7</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3286,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024NE0001121</t>
+          <t>2024NE0001122</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3530.7</v>
+        <v>33952.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3309,19 +3309,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2024NE0001120</t>
+          <t>2024NE0001123</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>18283.02</v>
+        <v>31184.56</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
@@ -3574,10 +3574,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2015NE01794</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>2015NE01796</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>15/10/2015</t>
@@ -3626,14 +3630,10 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2015NE01796</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2015NE01794</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>15/10/2015</t>
@@ -3686,10 +3686,14 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2016NE01053</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>2016NE01054</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
           <t>14/07/2016</t>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>anulação</t>
+          <t>SERVIÇO DE IMPLANTAÇÃO DE SOFTWARE</t>
         </is>
       </c>
     </row>
@@ -3742,14 +3746,10 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2016NE01054</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2016NE01053</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>14/07/2016</t>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SERVIÇO DE IMPLANTAÇÃO DE SOFTWARE</t>
+          <t>anulação</t>
         </is>
       </c>
     </row>
@@ -4112,12 +4112,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025NE0000239</t>
+          <t>2025NE0000238</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>33952.5</v>
+        <v>3530.7</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4135,19 +4135,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025NE0000237</t>
+          <t>2025NE0000241</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>18283.02</v>
+        <v>32513.02</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4202,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025NE0000241</t>
+          <t>2025NE0000237</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>32513.02</v>
+        <v>18283.02</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4225,19 +4225,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025NE0000238</t>
+          <t>2025NE0000239</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3530.7</v>
+        <v>33952.5</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
@@ -4288,10 +4288,14 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2016NE00734</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>2016NE00733</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9/2014</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>09/05/2016</t>
@@ -4307,21 +4311,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>Contratação de serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados, cuja descrição está contida no anexo que passa a fazer parte integrante do contrato</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2016NE00733</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>9/2014</t>
-        </is>
-      </c>
+          <t>2016NE00734</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>09/05/2016</t>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Contratação de serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados, cuja descrição está contida no anexo que passa a fazer parte integrante do contrato</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2024NE0000720</t>
+          <t>2024NE0000721</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3530.7</v>
+        <v>33952.5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4397,19 +4397,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2024NE0000719</t>
+          <t>2024NE0000717</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>18283.02</v>
+        <v>31184.56</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
@@ -4464,12 +4464,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024NE0000717</t>
+          <t>2024NE0000719</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>31184.56</v>
+        <v>18283.02</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4487,19 +4487,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024NE0000721</t>
+          <t>2024NE0000720</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>33952.5</v>
+        <v>3530.7</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4517,14 +4517,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2023NE0000479</t>
+          <t>2023NE00479</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Fornecimento de Software de comunicação VPN e Hospedagem de Sistema de Informação.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2023NE00479</t>
+          <t>2023NE0000479</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fornecimento de Software de comunicação VPN e Hospedagem de Sistema de Informação.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2022NE0000075</t>
+          <t>2022NE0000074</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>817.14</v>
+        <v>19975.87</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Serviços de processamento de dados de folha de pagamento especial do mês de setembro de 2021, sem contrato, Parecer Jurídico n.º 135/2021 e termo de Ajuste de Contas n.º 005/2021 publicado no Diário O</t>
+          <t>Serviços de tecnologia da informação e comunicação para migração de dados de geoprocessamento do IPAAM. Contrato n.º 012/2021.</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2022NE0000074</t>
+          <t>2022NE0000075</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>19975.87</v>
+        <v>817.14</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4693,19 +4693,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Serviços de tecnologia da informação e comunicação para migração de dados de geoprocessamento do IPAAM. Contrato n.º 012/2021.</t>
+          <t>Serviços de processamento de dados de folha de pagamento especial do mês de setembro de 2021, sem contrato, Parecer Jurídico n.º 135/2021 e termo de Ajuste de Contas n.º 005/2021 publicado no Diário O</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025NE0000523</t>
+          <t>2025NE0000524</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>9739.370000000001</v>
+        <v>294.23</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4723,19 +4723,19 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025NE0000522</t>
+          <t>2025NE0000526</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5180.29</v>
+        <v>11317.5</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4753,19 +4753,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025NE0000529</t>
+          <t>2025NE0000527</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>32513.02</v>
+        <v>18086.5</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4783,19 +4783,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025NE0000528</t>
+          <t>2025NE0000525</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1804.18</v>
+        <v>1880.8</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4813,19 +4813,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025NE0000525</t>
+          <t>2025NE0000528</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1880.8</v>
+        <v>1804.18</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025NE0000527</t>
+          <t>2025NE0000529</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>18086.5</v>
+        <v>32513.02</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4873,19 +4873,19 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025NE0000526</t>
+          <t>2025NE0000522</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11317.5</v>
+        <v>5180.29</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4903,19 +4903,19 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025NE0000524</t>
+          <t>2025NE0000523</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>294.23</v>
+        <v>9739.370000000001</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4966,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2024NE0001375</t>
+          <t>2024NE0001374</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>17151.54</v>
+        <v>33952.5</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4989,19 +4989,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2024NE0001376</t>
+          <t>2024NE0001373</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>865.23</v>
+        <v>3530.7</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2024NE0001373</t>
+          <t>2024NE0001376</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3530.7</v>
+        <v>865.23</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5079,19 +5079,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2024NE0001374</t>
+          <t>2024NE0001375</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>33952.5</v>
+        <v>17151.54</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5109,19 +5109,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026NE0000008</t>
+          <t>2026NE0000007</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>14/2025</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>130958.4</v>
+        <v>3766.76</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5139,19 +5139,19 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação, compreendendo a hospedagem de sistemas de informação em ambiente de infraestrutura virtualizada, para comport</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026NE0000007</t>
+          <t>2026NE0000008</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>14/2025</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3766.76</v>
+        <v>130958.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5169,19 +5169,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação, compreendendo a hospedagem de sistemas de informação em ambiente de infraestrutura virtualizada, para comport</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2015NE00020</t>
+          <t>2015NE00021</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1/2011</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5199,19 +5199,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>CONTRATOS PARA SERVIÇOS DE INFORMÁTICA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2015NE00033</t>
+          <t>2015NE00018</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>1/2011</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015</t>
+          <t>CONTRATOS PARA SERVIÇOS DE INFORMATICA</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2015NE00018</t>
+          <t>2015NE00033</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1/2011</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5289,19 +5289,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CONTRATOS PARA SERVIÇOS DE INFORMATICA</t>
+          <t>Cobertura financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2015NE00021</t>
+          <t>2015NE00020</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>1/2011</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CONTRATOS PARA SERVIÇOS DE INFORMÁTICA</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025NE0001396</t>
+          <t>2025NE0001395</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>902.0700000000001</v>
+        <v>36173</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5409,19 +5409,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025NE0001397</t>
+          <t>2025NE0001394</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>17882.2</v>
+        <v>3761.6</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
@@ -5476,12 +5476,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025NE0001394</t>
+          <t>2025NE0001397</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3761.6</v>
+        <v>17882.2</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5499,19 +5499,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025NE0001395</t>
+          <t>2025NE0001396</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>36173</v>
+        <v>902.0700000000001</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
@@ -5596,12 +5596,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2018NE00397</t>
+          <t>2018NE00396</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>120600</v>
+        <v>8033.19</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5626,12 +5626,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2018NE00396</t>
+          <t>2018NE00397</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8033.19</v>
+        <v>120600</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5682,12 +5682,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021NE0000001</t>
+          <t>2021NE0000007</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>240810.24</v>
+        <v>15027.58</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5705,19 +5705,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede do Governo, de forma eventual.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de implantação e execução de sistema de protocolo em plataforma Web (SPROweb), objetivando o controle e acompanhamento do registro de todo</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021NE0000007</t>
+          <t>2021NE0000001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>15027.58</v>
+        <v>240810.24</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5735,19 +5735,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de implantação e execução de sistema de protocolo em plataforma Web (SPROweb), objetivando o controle e acompanhamento do registro de todo</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede do Governo, de forma eventual.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2016NE00032</t>
+          <t>2016NE00031</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>10758.63</v>
+        <v>174600</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5765,19 +5765,19 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE INFORMATICA</t>
+          <t>SERVIÇOS DE INFORMÁTICA</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2016NE00031</t>
+          <t>2016NE00032</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>174600</v>
+        <v>10758.63</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE INFORMÁTICA</t>
+          <t>SERVIÇOS DE INFORMATICA</t>
         </is>
       </c>
     </row>
@@ -5858,14 +5858,10 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025NE0000887</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>18/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000884</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>03/07/2025</t>
@@ -5881,17 +5877,21 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Anulação da NE de Reforço nº 861 para ajuste na vigência</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025NE0000884</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+          <t>2025NE0000887</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>18/2021</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr">
         <is>
           <t>03/07/2025</t>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Anulação da NE de Reforço nº 861 para ajuste na vigência</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5944,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2022NE0000018</t>
+          <t>2022NE0000016</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>25173.09</v>
+        <v>87984.03</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de implantação e execução de Sistema de Protocolo em plataforma Web (Sproweb), objetivando o controle e acompanhamento de registro de docu</t>
+          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistema de informação em infraestrutura virtualizada, para comportar o sistema </t>
         </is>
       </c>
     </row>
@@ -6004,12 +6004,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2022NE0000016</t>
+          <t>2022NE0000018</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>87984.03</v>
+        <v>25173.09</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6027,19 +6027,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistema de informação em infraestrutura virtualizada, para comportar o sistema </t>
+          <t>Contratação de empresa especializada na prestação de serviços de implantação e execução de Sistema de Protocolo em plataforma Web (Sproweb), objetivando o controle e acompanhamento de registro de docu</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025NE0001280</t>
+          <t>2025NE0001277</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>32513.02</v>
+        <v>3761.6</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6057,19 +6057,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025NE0001279</t>
+          <t>2025NE0001276</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1804.18</v>
+        <v>19478.74</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025NE0001276</t>
+          <t>2025NE0001279</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>19478.74</v>
+        <v>1804.18</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6147,19 +6147,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025NE0001277</t>
+          <t>2025NE0001280</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3761.6</v>
+        <v>32513.02</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6177,17 +6177,21 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025NE0000866</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
+          <t>2025NE0000868</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>7/2021</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>02/07/2025</t>
@@ -6203,21 +6207,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Anulação para correção da data de vigência</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025NE0000868</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>7/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000866</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>02/07/2025</t>
@@ -6233,28 +6233,24 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
+          <t>Anulação para correção da data de vigência</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2018NE00392</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>9/2014</t>
-        </is>
-      </c>
+          <t>2018NE00390</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
           <t>02/04/2018</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>19969.99</v>
+        <v>8033.19</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6263,7 +6259,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados pelo período de 12 meses.</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
@@ -6296,17 +6292,21 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2018NE00390</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
+          <t>2018NE00392</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>9/2014</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>02/04/2018</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>8033.19</v>
+        <v>19969.99</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6315,19 +6315,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>Contratação de empresa especializada em serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados pelo período de 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025NE0000009</t>
+          <t>2025NE0000011</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>33952.5</v>
+        <v>32513.02</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025NE0000011</t>
+          <t>2025NE0000009</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>32513.02</v>
+        <v>33952.5</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6405,19 +6405,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2024NE0000011</t>
+          <t>2024NE0000007</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1730.46</v>
+        <v>18283.02</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6435,19 +6435,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2024NE0000007</t>
+          <t>2024NE0000011</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>18283.02</v>
+        <v>1730.46</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6465,19 +6465,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM. PARECER/IPAAM/PAD/DJ N.º 1</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2023NE0000011</t>
+          <t>2023NE0000001</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>14/2020</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>9300.690000000001</v>
+        <v>230765.78</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6495,19 +6495,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2023NE0000018</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>18/2021</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>52784.92</v>
+        <v>12690.04</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6525,19 +6525,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2023NE0000015</t>
+          <t>2023NE0000017</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>14/2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>100215.18</v>
+        <v>20034.37</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6555,19 +6555,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação e comunicação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada para atende</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a disponibilização do sistema informatizado de agendamento via WEB para dar suporte ao agendame</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2023NE0000017</t>
+          <t>2023NE0000015</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>14/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>20034.37</v>
+        <v>100215.18</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6585,19 +6585,19 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a disponibilização do sistema informatizado de agendamento via WEB para dar suporte ao agendame</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação e comunicação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada para atende</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000018</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>18/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>12690.04</v>
+        <v>52784.92</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6615,19 +6615,19 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de implantação e execução de sistemas de protocolo em plataforma (Sproweb) para controle de documentos e processos do IPAAM.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2023NE0000001</t>
+          <t>2023NE0000011</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>14/2020</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>230765.78</v>
+        <v>9300.690000000001</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6645,14 +6645,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2020NE00006</t>
+          <t>2020NE00010</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>201352.89</v>
+        <v>15027.58</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de implantação e execução de sistema de protocolo em plataforma Web (SPROWeb) objetivando o controle e acompanhamento do registro de todos</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2020NE00010</t>
+          <t>2020NE00006</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>15027.58</v>
+        <v>201352.89</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6735,24 +6735,28 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de implantação e execução de sistema de protocolo em plataforma Web (SPROWeb) objetivando o controle e acompanhamento do registro de todos</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2019NE00031</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr"/>
+          <t>2019NE00015</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>12708.14</v>
+        <v>13831.17</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6761,19 +6765,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA ACERTO</t>
+          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de execução para processamento do sistema de protocolo em plataforma Web (SPROWeb) para controle e acompanhamento de registro de todos os </t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2019NE00032</t>
+          <t>2019NE00017</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6782,7 +6786,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>12708.14</v>
+        <v>189026.91</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6791,19 +6795,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados, para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2019NE00018</t>
+          <t>2019NE00016</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6812,7 +6816,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>12708.14</v>
+        <v>13406.81</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6821,19 +6825,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados, para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada nos serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo Web, para publicação de informações, notícias, víde</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2019NE00016</t>
+          <t>2019NE00018</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6842,7 +6846,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>13406.81</v>
+        <v>12708.14</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6851,19 +6855,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada nos serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo Web, para publicação de informações, notícias, víde</t>
+          <t>Contratação de empresa especializada em serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados, para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2019NE00017</t>
+          <t>2019NE00032</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6872,7 +6876,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>189026.91</v>
+        <v>12708.14</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6881,28 +6885,24 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada em serviços de informática de forma eventual, mediante a utilização de pessoal e equipamentos adequados, para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2019NE00015</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+          <t>2019NE00031</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>13831.17</v>
+        <v>12708.14</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6911,19 +6911,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de execução para processamento do sistema de protocolo em plataforma Web (SPROWeb) para controle e acompanhamento de registro de todos os </t>
+          <t>ANULAÇÃO TOTAL PARA ACERTO</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2018NE00018</t>
+          <t>2018NE00040</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>13536.53</v>
+        <v>12528.54</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6941,19 +6941,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da informação, incluindo aquisição de softwares, licenças, implantação, manutenção, capacitação e suporte técnico.</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviços de licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de Conteúdo WEB ao Instituto de Proteção Ambiental do Amazonas, </t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2018NE00046</t>
+          <t>2018NE00027</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>293640.88</v>
+        <v>174600</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em desenvolvimento de sistema de informações geográficas com base em plataforma Esri (ArcGIS) conforme Projeto Básico.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, para atender as necessidades do IPAAM.</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2018NE00027</t>
+          <t>2018NE00046</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>174600</v>
+        <v>293640.88</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7031,19 +7031,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, para atender as necessidades do IPAAM.</t>
+          <t>Contratação de empresa especializada em desenvolvimento de sistema de informações geográficas com base em plataforma Esri (ArcGIS) conforme Projeto Básico.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2018NE00040</t>
+          <t>2018NE00018</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>12528.54</v>
+        <v>13536.53</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviços de licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de Conteúdo WEB ao Instituto de Proteção Ambiental do Amazonas, </t>
+          <t>Contratação de serviços de tecnologia da informação, incluindo aquisição de softwares, licenças, implantação, manutenção, capacitação e suporte técnico.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2017NE00027</t>
+          <t>2017NE00021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>12343.26</v>
+        <v>13133.33</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7091,19 +7091,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS</t>
+          <t>OUTROS SERVIÇOS DE TERCEIROS PESSOA JURÍDICA</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2017NE00029</t>
+          <t>2017NE00028</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>15060</v>
+        <v>12059.37</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS</t>
+          <t>DESPESAS DE TELEPROCESSAMENTO</t>
         </is>
       </c>
     </row>
@@ -7158,12 +7158,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2017NE00028</t>
+          <t>2017NE00029</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>12059.37</v>
+        <v>15060</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7181,19 +7181,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>DESPESAS DE TELEPROCESSAMENTO</t>
+          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2017NE00021</t>
+          <t>2017NE00027</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>13133.33</v>
+        <v>12343.26</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>OUTROS SERVIÇOS DE TERCEIROS PESSOA JURÍDICA</t>
+          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2017NE01352</t>
+          <t>2017NE01353</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>12059.37</v>
+        <v>10867.97</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7267,14 +7267,14 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE SALDO</t>
+          <t>ANULAÇÃO DE SALDO NÃO UTILIZADO</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2017NE01353</t>
+          <t>2017NE01352</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>10867.97</v>
+        <v>12059.37</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7293,19 +7293,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE SALDO NÃO UTILIZADO</t>
+          <t>ANULAÇÃO DE SALDO</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025NE0000858</t>
+          <t>2025NE0000859</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>8/2021</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>19478.74</v>
+        <v>3761.6</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7323,19 +7323,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025NE0000862</t>
+          <t>2025NE0000860</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>14/2021</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>32513.02</v>
+        <v>36173</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
+          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
         </is>
       </c>
     </row>
@@ -7390,12 +7390,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025NE0000860</t>
+          <t>2025NE0000862</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>14/2021</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>36173</v>
+        <v>32513.02</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7413,19 +7413,19 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de tecnologia da informação, compreendendo a hospedagem de sistemas de informação em infraestrutura virtualizada, para atender as necessid</t>
+          <t>Contratação de empresa especializada na prestação de serviços de rede, compreendendo o acesso gerenciado à internet, através da Rede de Governo, de forma eventual, para atender as necessidades do IPAA</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025NE0000859</t>
+          <t>2025NE0000858</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>3761.6</v>
+        <v>19478.74</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo WEB, para atender as necessidades do IP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de informática de forma eventual, para atender as necessidades do IPAAM. PARECER/IPAAM/PAD/DJ N.º 030/2023. TC: 0007/2021 AD: 05.</t>
         </is>
       </c>
     </row>
